--- a/pipeline/credit_rating/output/visrating_xhtn_20261003.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20261003.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -719,7 +719,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -800,7 +800,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -877,7 +877,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2661,7 +2661,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3999,7 +3999,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7798,7 +7798,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q112" s="1" t="n">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q113" s="1" t="n">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q114" s="1" t="n">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q115" s="1" t="n">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-10-03 09:23:53</t>
+          <t>2026-10-03 13:38:04</t>
         </is>
       </c>
       <c r="Q116" s="1" t="n">
